--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +914,126 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/92181008</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136660858</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103637</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>sågenvägen2, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>548207</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6626736</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket stor och helt frisk. Står i närheten av andra äldre, mycket grova, skyddsvärda träd i ett lövskogsbestånd</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elisabet Hultberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elisabet Hultberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136660858</t>
         </is>
       </c>
     </row>
@@ -921,6 +1041,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136660858</v>
       </c>
       <c r="B4" t="n">
-        <v>103637</v>
+        <v>103640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136660858</v>
       </c>
       <c r="B4" t="n">
-        <v>103640</v>
+        <v>103641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -919,41 +919,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136660858</v>
+        <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>103641</v>
+        <v>101463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -962,14 +970,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>sågenvägen2, Vstm</t>
+          <t>trolldruva, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548207</v>
+        <v>548185</v>
       </c>
       <c r="R4" t="n">
-        <v>6626736</v>
+        <v>6626611</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,17 +1004,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket stor och helt frisk. Står i närheten av andra äldre, mycket grova, skyddsvärda träd i ett lövskogsbestånd</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,6 +1035,126 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136799782</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136660858</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103646</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>sågenvägen2, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>548207</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6626736</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket stor och helt frisk. Står i närheten av andra äldre, mycket grova, skyddsvärda träd i ett lövskogsbestånd</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elisabet Hultberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elisabet Hultberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136660858</t>
         </is>
@@ -1042,6 +1165,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103646</v>
+        <v>103648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103648</v>
+        <v>103654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103654</v>
+        <v>103656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103656</v>
+        <v>103657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103657</v>
+        <v>103663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497421</v>
       </c>
       <c r="B2" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103663</v>
+        <v>103667</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103667</v>
+        <v>103669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103669</v>
+        <v>103671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103671</v>
+        <v>103684</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103684</v>
+        <v>103686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -957,11 +957,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>136660858</v>
       </c>
       <c r="B5" t="n">
-        <v>103686</v>
+        <v>103689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101506</v>
+        <v>101521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101522</v>
+        <v>101527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101527</v>
+        <v>101530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136799782</v>
       </c>
       <c r="B4" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,27 +795,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92181008</v>
+        <v>137414771</v>
       </c>
       <c r="B3" t="n">
-        <v>104628</v>
+        <v>107142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,31 +828,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillsjön Färna, Vstm</t>
+          <t>sågenvägen4, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548228</v>
+        <v>548182</v>
       </c>
       <c r="R3" t="n">
-        <v>6626780</v>
+        <v>6626640</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,12 +868,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-04-04</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-04-04</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ungträd, självföryngrad, vid våtmarkens kant mot fd väg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,35 +901,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Åravin</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tina Nordberg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tina Nordberg, Kenneth Nordberg</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92181008</t>
+          <t>https://artportalen.se/Sighting/137414771</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136799782</v>
+        <v>92181008</v>
       </c>
       <c r="B4" t="n">
-        <v>101536</v>
+        <v>104628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,16 +932,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,7 +951,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,23 +959,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>trolldruva, Vstm</t>
+          <t>Lillsjön Färna, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548185</v>
+        <v>548228</v>
       </c>
       <c r="R4" t="n">
-        <v>6626611</v>
+        <v>6626780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,12 +1002,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2021-04-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2021-04-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,60 +1020,69 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Åravin</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elisabet Hultberg</t>
+          <t>Tina Nordberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elisabet Hultberg</t>
+          <t>Tina Nordberg, Kenneth Nordberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799782</t>
+          <t>https://artportalen.se/Sighting/92181008</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136660858</v>
+        <v>136799782</v>
       </c>
       <c r="B5" t="n">
-        <v>103689</v>
+        <v>101536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223246</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
@@ -1081,14 +1092,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>sågenvägen2, Vstm</t>
+          <t>trolldruva, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548207</v>
+        <v>548185</v>
       </c>
       <c r="R5" t="n">
-        <v>6626736</v>
+        <v>6626611</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,17 +1126,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mycket stor och helt frisk. Står i närheten av andra äldre, mycket grova, skyddsvärda träd i ett lövskogsbestånd</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,7 +1158,243 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136799782</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136660858</v>
+      </c>
+      <c r="B6" t="n">
+        <v>103689</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>sågenvägen2, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>548207</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6626736</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mycket stor och helt frisk. Står i närheten av andra äldre, mycket grova, skyddsvärda träd i ett lövskogsbestånd</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elisabet Hultberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elisabet Hultberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136660858</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137414897</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103720</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>sågenvägen4, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>548182</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6626640</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elisabet Hultberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elisabet Hultberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137414897</t>
         </is>
       </c>
     </row>
@@ -1162,6 +1404,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137414771</v>
       </c>
       <c r="B3" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>137414897</v>
       </c>
       <c r="B7" t="n">
-        <v>103720</v>
+        <v>103732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137414771</v>
       </c>
       <c r="B3" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>137414897</v>
       </c>
       <c r="B7" t="n">
-        <v>103732</v>
+        <v>103733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137414771</v>
       </c>
       <c r="B3" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>137414897</v>
       </c>
       <c r="B7" t="n">
-        <v>103733</v>
+        <v>103736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34303-2026 artfynd.xlsx
+++ b/artfynd/A 34303-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137414771</v>
       </c>
       <c r="B3" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>137414897</v>
       </c>
       <c r="B7" t="n">
-        <v>103736</v>
+        <v>103741</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
